--- a/Lumbee_RIVR_TBCP_Agreement_Package/05_Schedules/S8_Subscriber_Payment_Revenue_ProgramIncome_Tax_Audit.xlsx
+++ b/Lumbee_RIVR_TBCP_Agreement_Package/05_Schedules/S8_Subscriber_Payment_Revenue_ProgramIncome_Tax_Audit.xlsx
@@ -1404,9 +1404,10 @@
         <f>IF(AND(ISNUMBER(B6),ISNUMBER(B7)),B6*B7,"")</f>
         <v/>
       </c>
-      <c r="C8" s="14">
-        <f> Subscribers x Rate</f>
-        <v/>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Subscribers x Rate</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1419,9 +1420,10 @@
         <f>IF(ISNUMBER(B8),B8*12,"")</f>
         <v/>
       </c>
-      <c r="C9" s="14">
-        <f> Monthly x 12</f>
-        <v/>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Monthly x 12</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Lumbee_RIVR_TBCP_Agreement_Package/05_Schedules/S8_Subscriber_Payment_Revenue_ProgramIncome_Tax_Audit.xlsx
+++ b/Lumbee_RIVR_TBCP_Agreement_Package/05_Schedules/S8_Subscriber_Payment_Revenue_ProgramIncome_Tax_Audit.xlsx
@@ -564,6 +564,14 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Lumbee Tribe”); LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”); Lumbee River Electric Membership Corporation d/b/a Lumbee River EMC (“LREMC”), separate asset owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -692,6 +700,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
